--- a/data/trans_orig/IP26B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP26B-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15875</t>
+          <t>15190</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5452</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16018</t>
+          <t>16122</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12859</t>
+          <t>12836</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27880</t>
+          <t>27761</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34056</t>
+          <t>34314</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52270</t>
+          <t>51708</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30551</t>
+          <t>30618</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47642</t>
+          <t>48013</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69334</t>
+          <t>68452</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94132</t>
+          <t>93363</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69753</t>
+          <t>70420</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>90039</t>
+          <t>89037</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>88920</t>
+          <t>88623</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>108552</t>
+          <t>107298</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>165401</t>
+          <t>164328</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>191069</t>
+          <t>191638</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>66,02%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4551</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8689</t>
+          <t>9247</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2489</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9838</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2079</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>8989</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>11513</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8691</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19406</t>
+          <t>20059</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>14664</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28779</t>
+          <t>27937</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26102</t>
+          <t>26702</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43820</t>
+          <t>43735</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61522</t>
+          <t>61979</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81382</t>
+          <t>81916</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62428</t>
+          <t>62610</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83183</t>
+          <t>84380</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>130517</t>
+          <t>127871</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>158842</t>
+          <t>158380</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,94%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81641</t>
+          <t>82459</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103868</t>
+          <t>103509</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>85632</t>
+          <t>85862</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>108871</t>
+          <t>109026</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>175697</t>
+          <t>175496</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>205405</t>
+          <t>206605</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,8%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11535</t>
+          <t>11116</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24181</t>
+          <t>23754</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9165</t>
+          <t>8657</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20400</t>
+          <t>20530</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23480</t>
+          <t>23038</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41050</t>
+          <t>38609</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3542</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12373</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12885</t>
+          <t>12984</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13032</t>
+          <t>12782</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5192</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15042</t>
+          <t>14790</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>11813</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24193</t>
+          <t>24943</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32579</t>
+          <t>32449</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49407</t>
+          <t>48264</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32637</t>
+          <t>32117</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>49308</t>
+          <t>48697</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69641</t>
+          <t>69713</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>93283</t>
+          <t>93582</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>62046</t>
+          <t>62156</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>79869</t>
+          <t>79514</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>65526</t>
+          <t>66349</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>84616</t>
+          <t>85739</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>132513</t>
+          <t>133080</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>158931</t>
+          <t>159267</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,62%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9692</t>
+          <t>9564</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20468</t>
+          <t>20321</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12660</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25078</t>
+          <t>25229</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25091</t>
+          <t>25300</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41531</t>
+          <t>41331</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10579</t>
+          <t>10041</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15061</t>
+          <t>15547</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15338</t>
+          <t>15740</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31230</t>
+          <t>30982</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9774</t>
+          <t>9734</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21412</t>
+          <t>22771</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28277</t>
+          <t>29161</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48400</t>
+          <t>48860</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>59383</t>
+          <t>59262</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>82299</t>
+          <t>82796</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>63626</t>
+          <t>62917</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>85720</t>
+          <t>85328</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>128234</t>
+          <t>127371</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>160065</t>
+          <t>159793</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,37%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>87837</t>
+          <t>87970</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>111628</t>
+          <t>111968</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>88935</t>
+          <t>88686</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>112665</t>
+          <t>112306</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>185119</t>
+          <t>183654</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>217225</t>
+          <t>217948</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,33%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6470</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17199</t>
+          <t>17493</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7395</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18873</t>
+          <t>18790</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16365</t>
+          <t>16752</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31631</t>
+          <t>32249</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>9446</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3311</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11941</t>
+          <t>11816</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6253</t>
+          <t>6830</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17143</t>
+          <t>17642</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>43458</t>
+          <t>42811</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>65360</t>
+          <t>65846</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>43838</t>
+          <t>43171</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>67985</t>
+          <t>67484</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>91369</t>
+          <t>93284</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>124853</t>
+          <t>126252</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>206365</t>
+          <t>206134</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>244918</t>
+          <t>245191</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>206133</t>
+          <t>204672</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>246974</t>
+          <t>244689</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>423299</t>
+          <t>424794</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>481980</t>
+          <t>482486</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,47%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>323542</t>
+          <t>322592</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>364153</t>
+          <t>363332</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>350612</t>
+          <t>349122</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>391074</t>
+          <t>393685</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>683596</t>
+          <t>687107</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>744272</t>
+          <t>743408</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>53,11%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>34200</t>
+          <t>33535</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>53846</t>
+          <t>54832</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>38744</t>
+          <t>37786</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>59467</t>
+          <t>59853</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>77175</t>
+          <t>76752</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>107317</t>
+          <t>107111</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>21528</t>
+          <t>20205</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13788</t>
+          <t>13552</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28075</t>
+          <t>28213</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>25990</t>
+          <t>25727</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>45148</t>
+          <t>44639</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12421</t>
+          <t>12361</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14447</t>
+          <t>14150</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10217</t>
+          <t>11122</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23563</t>
+          <t>23843</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17665</t>
+          <t>17988</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33123</t>
+          <t>33384</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22337</t>
+          <t>22546</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38567</t>
+          <t>40291</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44095</t>
+          <t>43770</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66233</t>
+          <t>65695</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79294</t>
+          <t>79086</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>98588</t>
+          <t>98293</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74041</t>
+          <t>74160</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>94011</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>158618</t>
+          <t>159800</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>187582</t>
+          <t>188442</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,65%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7264</t>
+          <t>7413</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18690</t>
+          <t>17999</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17095</t>
+          <t>16704</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32701</t>
+          <t>32101</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27391</t>
+          <t>27831</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46496</t>
+          <t>46817</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2093</t>
+          <t>2591</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10094</t>
+          <t>9757</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11863</t>
+          <t>12299</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18017</t>
+          <t>18153</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>7977</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18325</t>
+          <t>18547</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13576</t>
+          <t>14150</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27659</t>
+          <t>28077</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24615</t>
+          <t>24930</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41567</t>
+          <t>42174</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33212</t>
+          <t>32933</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50681</t>
+          <t>51233</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26921</t>
+          <t>27512</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44926</t>
+          <t>44365</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64192</t>
+          <t>64281</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>90758</t>
+          <t>89286</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>109187</t>
+          <t>108002</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>130240</t>
+          <t>130950</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>119726</t>
+          <t>120686</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>142615</t>
+          <t>143545</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>234825</t>
+          <t>234566</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>267013</t>
+          <t>267052</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,65%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20464</t>
+          <t>20416</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36474</t>
+          <t>36330</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18525</t>
+          <t>18596</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33942</t>
+          <t>34967</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41714</t>
+          <t>42091</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63857</t>
+          <t>64418</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9697</t>
+          <t>8963</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14780</t>
+          <t>14401</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>8446</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21018</t>
+          <t>20645</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7298</t>
+          <t>6982</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18127</t>
+          <t>17301</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6611</t>
+          <t>6299</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17305</t>
+          <t>17748</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15934</t>
+          <t>16218</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32224</t>
+          <t>31212</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15867</t>
+          <t>15585</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29457</t>
+          <t>29089</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>14866</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27977</t>
+          <t>28861</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34307</t>
+          <t>33810</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53403</t>
+          <t>52406</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>86381</t>
+          <t>86704</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>105649</t>
+          <t>105835</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>97556</t>
+          <t>98722</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>117236</t>
+          <t>117384</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>190144</t>
+          <t>191130</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>217884</t>
+          <t>218655</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>68,04%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16658</t>
+          <t>16321</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30430</t>
+          <t>30858</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>16053</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29912</t>
+          <t>30775</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35718</t>
+          <t>35048</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55818</t>
+          <t>54871</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>539</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6198</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1665</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>8885</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11758</t>
+          <t>11862</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10097</t>
+          <t>10229</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23643</t>
+          <t>22706</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5971</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17413</t>
+          <t>17888</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,47 +6470,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>8,62%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>25886</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>18351</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>35013</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>6,2%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>8,39%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>25886</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>18196</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>34436</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>6,2%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13692</t>
+          <t>13944</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>29647</t>
+          <t>28648</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18075</t>
+          <t>17627</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>33866</t>
+          <t>33242</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>36023</t>
+          <t>35794</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>58630</t>
+          <t>57479</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>121190</t>
+          <t>122937</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>144799</t>
+          <t>145563</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>127893</t>
+          <t>128176</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>151176</t>
+          <t>152271</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>256201</t>
+          <t>259685</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>291622</t>
+          <t>291340</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,83%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27351</t>
+          <t>27401</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46615</t>
+          <t>45177</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16956</t>
+          <t>16817</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33491</t>
+          <t>32603</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>48435</t>
+          <t>48949</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>73766</t>
+          <t>72376</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>717</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13329</t>
+          <t>12982</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17671</t>
+          <t>16907</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>36195</t>
+          <t>36904</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>57669</t>
+          <t>58211</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>39899</t>
+          <t>40036</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>62621</t>
+          <t>61568</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>82182</t>
+          <t>82245</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>113079</t>
+          <t>113342</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>93959</t>
+          <t>93072</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>124048</t>
+          <t>123575</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>97729</t>
+          <t>95540</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>128231</t>
+          <t>127311</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>199452</t>
+          <t>198142</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>243748</t>
+          <t>243510</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>419102</t>
+          <t>416961</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>460534</t>
+          <t>458153</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,47 +7343,47 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
+          <t>58,89%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>64,71%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>464208</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>442850</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>486970</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>62,04%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
           <t>59,19%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>65,04%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>660</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>464208</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>440432</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>484480</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>62,04%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>58,87%</t>
-        </is>
-      </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>875414</t>
+          <t>870976</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>934704</t>
+          <t>933115</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,08%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>84730</t>
+          <t>84758</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>115960</t>
+          <t>114826</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>81177</t>
+          <t>80927</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>111423</t>
+          <t>111268</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>173734</t>
+          <t>174065</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>213997</t>
+          <t>216340</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10258</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>22860</t>
+          <t>23264</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>19063</t>
+          <t>19099</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>35545</t>
+          <t>36237</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>32788</t>
+          <t>33073</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>53419</t>
+          <t>54443</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3668</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12212</t>
+          <t>12892</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8513</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21230</t>
+          <t>20410</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13896</t>
+          <t>14068</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29152</t>
+          <t>28867</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30849</t>
+          <t>31804</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49428</t>
+          <t>48972</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33295</t>
+          <t>32761</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51917</t>
+          <t>51138</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68288</t>
+          <t>69480</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94813</t>
+          <t>94559</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,71%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47561</t>
+          <t>48033</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66585</t>
+          <t>67388</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>50168</t>
+          <t>49368</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>69002</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>104989</t>
+          <t>102213</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>132270</t>
+          <t>130419</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>46,5%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15307</t>
+          <t>14959</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30747</t>
+          <t>29705</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21049</t>
+          <t>21008</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38009</t>
+          <t>37147</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38819</t>
+          <t>39964</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61973</t>
+          <t>61819</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>2721</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11028</t>
+          <t>10513</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1423</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5381</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15780</t>
+          <t>16470</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21764</t>
+          <t>21855</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37336</t>
+          <t>37099</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19642</t>
+          <t>20357</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35529</t>
+          <t>37098</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45601</t>
+          <t>45894</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67866</t>
+          <t>67711</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53844</t>
+          <t>52223</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73826</t>
+          <t>72579</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55994</t>
+          <t>55561</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76262</t>
+          <t>77903</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>114131</t>
+          <t>112593</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>143622</t>
+          <t>144254</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,52%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>79315</t>
+          <t>79471</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>101080</t>
+          <t>102301</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>86599</t>
+          <t>86115</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>110481</t>
+          <t>109897</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>172815</t>
+          <t>171596</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>205571</t>
+          <t>205730</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,8%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14745</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28513</t>
+          <t>29081</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18810</t>
+          <t>18379</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33978</t>
+          <t>33684</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36019</t>
+          <t>37017</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56608</t>
+          <t>57528</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8912</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11668</t>
+          <t>11723</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17172</t>
+          <t>16427</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9828</t>
+          <t>9364</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2155</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8941</t>
+          <t>8259</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6123</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16181</t>
+          <t>15842</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24828</t>
+          <t>23786</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39744</t>
+          <t>39894</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20870</t>
+          <t>21039</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37293</t>
+          <t>37110</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>49853</t>
+          <t>49886</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71254</t>
+          <t>70941</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>77482</t>
+          <t>78047</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>96828</t>
+          <t>97758</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>83055</t>
+          <t>82941</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>103539</t>
+          <t>104446</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>169160</t>
+          <t>169211</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>196557</t>
+          <t>197213</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>61,33%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21381</t>
+          <t>20464</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35915</t>
+          <t>36052</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29288</t>
+          <t>29218</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46982</t>
+          <t>46909</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>54787</t>
+          <t>54752</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78284</t>
+          <t>78660</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -9837,7 +9837,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>579</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5490</t>
+          <t>5592</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1409</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8691</t>
+          <t>8168</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15441</t>
+          <t>15136</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2952</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11324</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10155</t>
+          <t>10427</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23141</t>
+          <t>22803</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29806</t>
+          <t>30395</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50340</t>
+          <t>49973</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30026</t>
+          <t>29759</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47496</t>
+          <t>48516</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>65827</t>
+          <t>65524</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>92504</t>
+          <t>92937</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>94877</t>
+          <t>95058</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>119595</t>
+          <t>118892</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>97360</t>
+          <t>98422</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>121331</t>
+          <t>122435</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>198806</t>
+          <t>199158</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>232090</t>
+          <t>232426</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,54%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>35066</t>
+          <t>34514</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55149</t>
+          <t>54950</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35645</t>
+          <t>35163</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>57116</t>
+          <t>56373</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>76901</t>
+          <t>76152</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>104568</t>
+          <t>104720</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2991</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11895</t>
+          <t>12797</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10457</t>
+          <t>11013</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>6229</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19182</t>
+          <t>18878</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>41239</t>
+          <t>40502</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>62186</t>
+          <t>62021</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>41120</t>
+          <t>41197</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>65391</t>
+          <t>64772</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>88528</t>
+          <t>87736</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>118930</t>
+          <t>118757</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>156700</t>
+          <t>154884</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>193112</t>
+          <t>193212</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>155658</t>
+          <t>155689</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>193661</t>
+          <t>193570</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>322963</t>
+          <t>321802</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>375382</t>
+          <t>375272</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>319840</t>
+          <t>320830</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>363187</t>
+          <t>363861</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>339596</t>
+          <t>337743</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>384117</t>
+          <t>385978</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>672752</t>
+          <t>674256</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>733485</t>
+          <t>735607</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,96%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>99880</t>
+          <t>99945</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>131860</t>
+          <t>132736</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>120872</t>
+          <t>120209</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>155140</t>
+          <t>153957</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>228038</t>
+          <t>228897</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>276008</t>
+          <t>276986</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12229</t>
+          <t>12108</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26758</t>
+          <t>26841</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11317</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25422</t>
+          <t>26181</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>26868</t>
+          <t>27806</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>45504</t>
+          <t>47258</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
